--- a/TextPad 7/TextPad_Test_Report_and_Bug_report_template.xlsx
+++ b/TextPad 7/TextPad_Test_Report_and_Bug_report_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opilane\source\repos\HenryKuningas\TarkvarasysteemideTestimine\TextPad 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B844F9E7-B5AD-4863-923B-92806B79698C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02E8FA7-C723-4375-9084-1313068E3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16410" yWindow="8535" windowWidth="23925" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11490" yWindow="7080" windowWidth="23925" windowHeight="12315" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Report" sheetId="11" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="53">
   <si>
     <t>Product:</t>
   </si>
@@ -204,31 +204,49 @@
     <t>Truncation 'Browse…' in 'Manage files' dialog</t>
   </si>
   <si>
+    <t>Truncation 'Bering Information' in 'About TextPad' dialog</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>4, 5</t>
+  </si>
+  <si>
+    <t>7, 8, 9, 10</t>
+  </si>
+  <si>
+    <t>11, 12</t>
+  </si>
+  <si>
+    <t>1, 2, 3</t>
+  </si>
+  <si>
     <t>Steps to reproduce: 
 1. Launch 'TextPad'
 2. Go to 'Help' -&gt; 'About TextPad'
 Expected result:
-There are no truncations
+There are no truncation
 Actual result: 
 There are truncations</t>
   </si>
   <si>
-    <t>Truncation 'Bering Information' in 'About TextPad' dialog</t>
-  </si>
-  <si>
-    <t>1, 2</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>4, 5</t>
-  </si>
-  <si>
-    <t>7, 8, 9, 10</t>
-  </si>
-  <si>
-    <t>11, 12</t>
+    <t>1.	Launch TextPad
+2.	Open any document containing text data
+3.	Go to File -&gt; Print… to invoke Print dialog 
+Expected result:
+There are no truncations
+Actual result:
+There are truncations</t>
+  </si>
+  <si>
+    <t>1.	Launch TextPad
+2.	Open any document containing text data
+3.	Go to File -&gt; Print… to invoke Print dialog 
+Expected result:
+There are no misalignments present
+Actual result:
+There are misalignments present</t>
   </si>
 </sst>
 </file>
@@ -1068,10 +1086,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Pilt 1">
+        <xdr:cNvPr id="3" name="Pilt 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0D89428-AAB7-4082-B818-A22E2AEDE127}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB9AEA2F-4E0B-4848-8ABA-C9A3BBAB46C1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1697,10 +1715,10 @@
         <v>21</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" s="34" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1711,10 +1729,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1738,7 +1756,7 @@
       </c>
       <c r="C5" s="22"/>
       <c r="D5" s="33" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1760,7 +1778,7 @@
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="35" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4193,7 +4211,7 @@
         <v>2</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="180.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4201,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="228.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4274,7 +4292,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="32" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="243" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -4284,7 +4304,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -4346,7 +4367,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="32" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -4577,6 +4600,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CBDF2EF6028720478E3F27B9B31ABD09" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af4c30ee4a8bd4ac003a3d536b29f91a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="615ccdff-0541-46ac-a88f-a8d1251c2b60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c50b0a04c06fbcee891037f18b70482d" ns2:_="">
     <xsd:import namespace="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
@@ -4716,22 +4754,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E4B81-85CB-4814-992F-9FCD036E17F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F20789A9-57E9-4886-B95B-F2A34AEE83F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37B6576-FA83-4FDB-AFBB-5436182600AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4747,28 +4794,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F20789A9-57E9-4886-B95B-F2A34AEE83F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E4B81-85CB-4814-992F-9FCD036E17F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/TextPad 7/TextPad_Test_Report_and_Bug_report_template.xlsx
+++ b/TextPad 7/TextPad_Test_Report_and_Bug_report_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opilane\source\repos\HenryKuningas\TarkvarasysteemideTestimine\TextPad 7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raud\Documents\GitHub\TarkvarasysteemideTestimine\TextPad 7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02E8FA7-C723-4375-9084-1313068E3CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9A1E96F-9C08-49C1-82B2-0A2211DECEFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11490" yWindow="7080" windowWidth="23925" windowHeight="12315" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="1657" windowWidth="28996" windowHeight="15675" tabRatio="869" firstSheet="14" activeTab="37" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Report" sheetId="11" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="58">
   <si>
     <t>Product:</t>
   </si>
@@ -247,6 +247,21 @@
 There are no misalignments present
 Actual result:
 There are misalignments present</t>
+  </si>
+  <si>
+    <t>Windows 11 Pro</t>
+  </si>
+  <si>
+    <t>Open files</t>
+  </si>
+  <si>
+    <t>Browse For Folder</t>
+  </si>
+  <si>
+    <t>On kohast natuke ära</t>
+  </si>
+  <si>
+    <t>Valge kuubik on seal kus number peaks olema</t>
   </si>
 </sst>
 </file>
@@ -693,7 +708,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normaallaad" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -932,17 +947,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>4896533</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>485843</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>239095</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>19561</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Pilt 1">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6E90972-990A-42D0-9FF1-403A9CE7F719}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA37041D-8942-4A04-B5A7-A4459BE0FC6D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -959,7 +974,301 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1409700" y="3448050"/>
-          <a:ext cx="4896533" cy="485843"/>
+          <a:ext cx="6954220" cy="3658111"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>248622</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>171955</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{459095BB-C21F-43D9-AFCD-1051D34A62C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6963747" cy="3620005"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>315732</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>38720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{312F439C-15D3-48EA-A6DD-B5C50AB47E91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="10078857" cy="4439270"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>277626</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76825</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E309A3-62FB-4449-AD88-6958844848FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="10040751" cy="4477375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>191889</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76798</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8483BC79-8CB1-4BBB-88D6-C0CC38A151CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="9955014" cy="4286848"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>229995</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02CE6316-9781-4248-8A5C-4DC7137CA707}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="9993120" cy="4401164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>268100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>181588</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6C5CFB3-AF1D-4840-B9B5-328DDB4E9C30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="10031225" cy="4391638"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1020,6 +1329,496 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>268100</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>124430</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{434D0EC2-58B1-458E-8512-54F0FDC9590E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="10031225" cy="4334480"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>258148</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>10087</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03381AAB-15EF-4DED-8973-A02014D30CD5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6973273" cy="4029637"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>381990</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>162482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7183F85-117E-479E-8601-DF6DB3DACCC7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7097115" cy="3991532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>343885</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>152956</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AFA50E97-9CE7-45FD-8406-F95EE32E30FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7059010" cy="3982006"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing24.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>448675</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>86298</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{008C24E2-7787-484E-8579-52ADF43176BD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7163800" cy="4105848"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing25.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>391517</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>19614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB66971-75FC-4437-8445-04C4F8B00BF9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7106642" cy="4039164"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing26.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>343885</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133903</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9F01522-1059-41C8-B8CF-61C29B3F0340}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7059010" cy="3962953"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing27.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3705742</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>86245</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DFAACD9-58E2-4BD0-AEE7-10DA1F1C0E9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="3705742" cy="3724795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing28.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5020376</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>153142</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{341DD49E-07A2-4523-8426-565432E8AA08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="5020376" cy="5315692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing29.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5068007</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>57879</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A127639-3D0D-44D0-A34A-C0D93451302D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="5068007" cy="5220429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1069,6 +1868,398 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>343885</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>20039</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{437E8B03-7B00-4306-BE3B-685DAB17F794}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="7059010" cy="7087589"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5744377</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>77038</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27420068-48F2-46AE-AB76-095D79C5904E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="5744377" cy="6001588"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>5630061</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>181801</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96E7428E-1C87-4A59-B123-08FD200E64F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="5630061" cy="5915851"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing33.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>486695</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>172407</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68146E20-5FED-4D56-B2D9-D404F61CAB7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6592220" cy="6858957"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing34.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>553379</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>86697</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9EC20CA-EBB9-4F5B-97BD-8E024C88EF66}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6658904" cy="6963747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing35.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>458116</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>153355</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{175F99E7-D69B-40D6-9974-E8D1E6CF18F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6563641" cy="6839905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing36.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>486695</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>67618</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69B3127D-E5B4-4E3B-BE92-B6403A3EF369}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6592220" cy="6754168"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing37.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>496221</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>162881</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F40B1AB-CE1A-4C77-B718-474BB42EA76B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1409700" y="3448050"/>
+          <a:ext cx="6601746" cy="6849431"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1364,7 +2555,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office'i kujundus">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2249,7 +3440,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2278,6 +3469,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2320,7 +3512,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2349,6 +3541,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2391,7 +3584,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2420,6 +3613,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2462,7 +3656,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2491,6 +3685,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2533,7 +3728,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2562,6 +3757,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2604,7 +3800,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2633,6 +3829,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2766,7 +3963,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2785,7 +3982,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -2795,6 +3994,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2837,7 +4037,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2856,7 +4056,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -2866,6 +4068,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2908,7 +4111,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -2937,6 +4140,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2979,7 +4183,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3008,6 +4212,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3050,7 +4255,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3079,6 +4284,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3121,7 +4327,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3193,7 +4399,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3222,6 +4428,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3264,7 +4471,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3293,6 +4500,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3335,7 +4543,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3354,7 +4562,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -3364,6 +4574,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3406,7 +4617,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3435,6 +4646,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3556,7 +4768,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3585,6 +4797,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3627,7 +4840,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3646,7 +4859,9 @@
       <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="9" spans="2:3" ht="241.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="7" t="s">
@@ -3656,6 +4871,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3698,7 +4914,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3727,6 +4943,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3769,7 +4986,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3798,6 +5015,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3840,7 +5058,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3869,6 +5087,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3911,7 +5130,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -3940,6 +5159,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3982,7 +5202,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -4011,6 +5231,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4053,7 +5274,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -4082,6 +5303,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4100,7 +5322,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="30">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
@@ -4124,7 +5346,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
@@ -4153,6 +5375,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4600,21 +5823,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100CBDF2EF6028720478E3F27B9B31ABD09" ma:contentTypeVersion="1" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af4c30ee4a8bd4ac003a3d536b29f91a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="615ccdff-0541-46ac-a88f-a8d1251c2b60" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c50b0a04c06fbcee891037f18b70482d" ns2:_="">
     <xsd:import namespace="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
@@ -4754,31 +5962,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E4B81-85CB-4814-992F-9FCD036E17F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F20789A9-57E9-4886-B95B-F2A34AEE83F1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37B6576-FA83-4FDB-AFBB-5436182600AB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4794,4 +5993,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F20789A9-57E9-4886-B95B-F2A34AEE83F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="615ccdff-0541-46ac-a88f-a8d1251c2b60"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C53E4B81-85CB-4814-992F-9FCD036E17F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>